--- a/BCI Disso Results.xlsx
+++ b/BCI Disso Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E7B258-C50D-44B1-BA93-57D59CF907E0}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD83722A-02AE-4C34-9642-50C820544E9A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EF8513EE-1635-4B6A-A69E-CD4E80FC268A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="53">
   <si>
     <t>SVM</t>
   </si>
@@ -85,13 +85,129 @@
   </si>
   <si>
     <t>CSP  + Random Forest</t>
+  </si>
+  <si>
+    <t>EEGNET</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">0.5951 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>± 0.03</t>
+    </r>
+  </si>
+  <si>
+    <t>0.5034 ± 0.016</t>
+  </si>
+  <si>
+    <t>0.006 ± 0.033</t>
+  </si>
+  <si>
+    <t>0.19 ±  0.066</t>
+  </si>
+  <si>
+    <t>0.639 ± 0.038</t>
+  </si>
+  <si>
+    <t>0.287 ± 0.067</t>
+  </si>
+  <si>
+    <t>0.639 ± 0.025</t>
+  </si>
+  <si>
+    <t>0.278 ± 0.05</t>
+  </si>
+  <si>
+    <t>0.659 ± 0.016</t>
+  </si>
+  <si>
+    <t>0.318 ± 0.033</t>
+  </si>
+  <si>
+    <t>0.643 ± 0.0335</t>
+  </si>
+  <si>
+    <t>0.534 ± 0.018</t>
+  </si>
+  <si>
+    <t>0.068 ± 0.036</t>
+  </si>
+  <si>
+    <t>0.499 ± 0.015</t>
+  </si>
+  <si>
+    <t>`-0.0006 ± 0.031</t>
+  </si>
+  <si>
+    <t>0.573 ± 0.030</t>
+  </si>
+  <si>
+    <t>0.147 ± 0.0592</t>
+  </si>
+  <si>
+    <t>0.513 ± 0.021</t>
+  </si>
+  <si>
+    <t>0.0267 ± 0.0433</t>
+  </si>
+  <si>
+    <t>0.941 ± 0.011</t>
+  </si>
+  <si>
+    <t>0.882 ± 0.022</t>
+  </si>
+  <si>
+    <t>0.798 ± 0.028</t>
+  </si>
+  <si>
+    <t>0.597 ± 0.056</t>
+  </si>
+  <si>
+    <t>0.768 ± 0.024</t>
+  </si>
+  <si>
+    <t>0.239 ± 0.097</t>
+  </si>
+  <si>
+    <t>0.6977 ± 0.023</t>
+  </si>
+  <si>
+    <t>0.017 ± 0.058</t>
+  </si>
+  <si>
+    <t>0.675 ±  0.0</t>
+  </si>
+  <si>
+    <t>0.63 ± 0.0</t>
+  </si>
+  <si>
+    <t>1 ± 0.0</t>
+  </si>
+  <si>
+    <t>0.751 ± 0.003</t>
+  </si>
+  <si>
+    <t>0.0107 ± 0.0182</t>
+  </si>
+  <si>
+    <t>0.750 ± 0.002</t>
+  </si>
+  <si>
+    <t>0.0106 ± 0.0180</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +222,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -128,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -137,6 +259,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -452,16 +580,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D345A3-9912-4709-8DAD-32A45ED1A3EA}">
-  <dimension ref="A2:O33"/>
+  <dimension ref="A2:R33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="3.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
     <col min="15" max="15" width="15.5703125" customWidth="1"/>
+    <col min="16" max="16" width="3.28515625" customWidth="1"/>
+    <col min="17" max="17" width="16.85546875" customWidth="1"/>
+    <col min="18" max="18" width="16.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
@@ -478,8 +613,12 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" s="6"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
@@ -500,8 +639,10 @@
         <v>14</v>
       </c>
       <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -518,8 +659,10 @@
         <v>1</v>
       </c>
       <c r="M4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
@@ -556,8 +699,14 @@
       <c r="O5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -600,8 +749,14 @@
       <c r="O6">
         <v>0.58499999999999996</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -642,8 +797,14 @@
       <c r="O7">
         <v>6.2E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -686,8 +847,14 @@
       <c r="O8">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q8" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -728,8 +895,14 @@
       <c r="O9">
         <v>-0.02</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
@@ -772,8 +945,14 @@
       <c r="O10">
         <v>0.81899999999999995</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q10" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
         <v>10</v>
@@ -814,8 +993,14 @@
       <c r="O11">
         <v>0.111</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -858,8 +1043,14 @@
       <c r="O12">
         <v>0.69399999999999995</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
@@ -900,8 +1091,14 @@
       <c r="O13">
         <v>0.13100000000000001</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q13" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
@@ -944,8 +1141,14 @@
       <c r="O14">
         <v>0.83399999999999996</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q14" t="s">
+        <v>34</v>
+      </c>
+      <c r="R14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="1" t="s">
         <v>10</v>
@@ -986,16 +1189,22 @@
       <c r="O15">
         <v>9.2999999999999999E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="Q15" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1006,8 +1215,12 @@
         <v>17</v>
       </c>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
         <v>0</v>
       </c>
@@ -1016,8 +1229,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1251,14 @@
       <c r="H21" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20191008</v>
       </c>
@@ -1062,8 +1283,14 @@
       <c r="H22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>38</v>
+      </c>
+      <c r="L22" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1086,8 +1313,14 @@
       <c r="H23">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1095,7 +1328,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>20191107</v>
       </c>
@@ -1120,8 +1353,14 @@
       <c r="H25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="1" t="s">
         <v>16</v>
@@ -1144,8 +1383,14 @@
       <c r="H26">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>20191203</v>
       </c>
@@ -1170,8 +1415,14 @@
       <c r="H28">
         <v>0.88</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>46</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1" t="s">
         <v>16</v>
@@ -1194,8 +1445,14 @@
       <c r="H29">
         <v>4.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K29" t="s">
+        <v>47</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>20200123</v>
       </c>
@@ -1220,8 +1477,14 @@
       <c r="H31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K31" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>20200206</v>
       </c>
@@ -1246,8 +1509,14 @@
       <c r="H32">
         <v>-0.02</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K32" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>20200220</v>
       </c>
@@ -1272,9 +1541,24 @@
       <c r="H33">
         <v>0.82</v>
       </c>
+      <c r="K33" t="s">
+        <v>51</v>
+      </c>
+      <c r="L33" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="J2:O2"/>
@@ -1291,13 +1575,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="A25:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BCI Disso Results.xlsx
+++ b/BCI Disso Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\# DISSERTATION\GitLab\ce901_venugopal_r\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD83722A-02AE-4C34-9642-50C820544E9A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6270284-4525-4C36-A89F-8C5E4C0D0D14}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EF8513EE-1635-4B6A-A69E-CD4E80FC268A}"/>
   </bookViews>
@@ -257,14 +257,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -600,47 +600,47 @@
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="Q2" s="5" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="Q2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="6"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
       <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="6"/>
       <c r="J3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="4"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
@@ -659,8 +659,8 @@
         <v>1</v>
       </c>
       <c r="M4" s="3"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
@@ -1215,10 +1215,10 @@
         <v>17</v>
       </c>
       <c r="H19" s="3"/>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L19" s="5"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
@@ -1229,8 +1229,8 @@
         <v>1</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
@@ -1550,15 +1550,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="K19:L20"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="J2:O2"/>
@@ -1575,6 +1566,15 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="K19:L20"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
